--- a/data/employees/EMP099/AST-EMP099-06.xlsx
+++ b/data/employees/EMP099/AST-EMP099-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Drew Kim (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Drew Kim | Role: Lead | Location: Portland | Date: 2025-04-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>91</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Automation backlog refinement. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62</v>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>91</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>71</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>95</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>88</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>64</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>71</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>95</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>98</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>91</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>70</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>64</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>88</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp099 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>74</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP099</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP099 contributes to ast emp099 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>